--- a/ds/planejamento/3semestre/planos/Plano_de_Ensino_PBE2.xlsx
+++ b/ds/planejamento/3semestre/planos/Plano_de_Ensino_PBE2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wellifabio\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEB772F-2763-45B2-AA0D-92ED1E75A3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9580D82-8A7B-47B5-8B53-738D3D3B6C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Turma: SESI 3º DES</t>
-  </si>
-  <si>
-    <t>Data :  21 / 01 / 2025</t>
   </si>
   <si>
     <t>Data:    /     /   2024</t>
@@ -277,6 +274,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Contextualização:
 </t>
@@ -286,6 +284,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Uma empresa fictícia do setor de serviços digitais precisa iniciar o desenvolvimento de um sistema back-end para atender aplicações cliente-servidor.
 O aluno foi contratado como desenvolvedor back-end júnior e deve preparar o ambiente, estruturar o sistema utilizando POO e disponibilizar uma API REST para comunicação com o cliente.
@@ -309,6 +308,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Desafios:
 </t>
@@ -318,6 +318,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>- Preparar corretamente o ambiente de desenvolvimento back-end
 - Estruturar o sistema utilizando Programação Orientada a Objetos
@@ -333,6 +334,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Entregas:
 </t>
@@ -342,6 +344,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>- Ambiente de desenvolvimento configurado e funcional
 - Projeto back-end criado em framework definido
@@ -498,6 +501,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Contextualização:
 </t>
@@ -507,6 +511,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Uma empresa do setor tecnológico necessita concluir o desenvolvimento de um sistema back-end completo, integrando persistência de dados, transferência de arquivos, organização arquitetural, documentação técnica e publicação da aplicação.
 O aluno atuará como desenvolvedor back-end, sendo responsável por finalizar, documentar e publicar a solução conforme os requisitos definidos.
@@ -528,6 +533,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Desafios:
 </t>
@@ -537,6 +543,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>- Implementar persistência de dados conforme regras de negócio
 - Realizar operações de transferência de arquivos
@@ -552,6 +559,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Entregas:
 </t>
@@ -561,6 +569,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>- Sistema back-end funcional e integrado ao banco de dados
 - Implementação de transferência de arquivos
@@ -663,6 +672,9 @@
   <si>
     <t>Carga Horária Presencial: 160</t>
   </si>
+  <si>
+    <t>Data :  21 / 01 / 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -684,136 +696,161 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="36"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1318,38 +1355,120 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1386,122 +1505,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1513,8 +1538,20 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1791,162 +1828,162 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="59" t="s">
+      <c r="B3" s="70"/>
+      <c r="C3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="60" t="s">
+      <c r="D3" s="70"/>
+      <c r="E3" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="61" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="61" t="s">
+      <c r="H3" s="63"/>
+      <c r="I3" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="46"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="62" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="69" t="s">
+      <c r="H4" s="40"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="40"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="48"/>
-    </row>
-    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="64" t="s">
+      <c r="D5" s="60"/>
+      <c r="E5" s="95" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="65" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="69" t="s">
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="40"/>
+    </row>
+    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="61"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="48"/>
-    </row>
-    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="66" t="s">
+      <c r="F6" s="57"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="63" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="87" t="s">
+      <c r="D7" s="60"/>
+      <c r="E7" s="97" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="60"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="70"/>
+    </row>
+    <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="61"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
+    </row>
+    <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="44"/>
-    </row>
-    <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="45"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="46"/>
-    </row>
-    <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="40"/>
+    </row>
+    <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="48"/>
-    </row>
-    <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="H10" s="40"/>
+      <c r="I10" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="48"/>
+      <c r="J10" s="40"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1972,26 +2009,26 @@
       <c r="B11" s="5">
         <v>6</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="73" t="s">
+      <c r="E11" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="F11" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="88" t="s">
+      <c r="G11" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="H11" s="60"/>
+      <c r="I11" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="42"/>
+      <c r="J11" s="60"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -2017,14 +2054,14 @@
       <c r="B12" s="5">
         <v>6</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="44"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="70"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -2050,14 +2087,14 @@
       <c r="B13" s="5">
         <v>6</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="44"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="70"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -2083,14 +2120,14 @@
       <c r="B14" s="5">
         <v>6</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="63"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -2116,24 +2153,24 @@
       <c r="B15" s="5">
         <v>6</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="73" t="s">
+      <c r="E15" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="73" t="s">
+      <c r="F15" s="52"/>
+      <c r="G15" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="41" t="s">
+      <c r="H15" s="60"/>
+      <c r="I15" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="42"/>
+      <c r="J15" s="60"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -2159,14 +2196,14 @@
       <c r="B16" s="5">
         <v>6</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="44"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="70"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2192,14 +2229,14 @@
       <c r="B17" s="5">
         <v>6</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="44"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="70"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -2225,14 +2262,14 @@
       <c r="B18" s="5">
         <v>6</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="44"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -2258,14 +2295,14 @@
       <c r="B19" s="5">
         <v>6</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="46"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="63"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -2291,24 +2328,24 @@
       <c r="B20" s="5">
         <v>6</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="79" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="E20" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="52"/>
+      <c r="G20" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="41" t="s">
+      <c r="H20" s="60"/>
+      <c r="I20" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="42"/>
+      <c r="J20" s="60"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -2334,14 +2371,14 @@
       <c r="B21" s="5">
         <v>6</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="44"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="70"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -2367,14 +2404,14 @@
       <c r="B22" s="5">
         <v>6</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="44"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="70"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -2400,14 +2437,14 @@
       <c r="B23" s="5">
         <v>6</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="63"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -2433,24 +2470,24 @@
       <c r="B24" s="5">
         <v>6</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="E24" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="F24" s="52"/>
+      <c r="G24" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="41" t="s">
+      <c r="H24" s="60"/>
+      <c r="I24" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="42"/>
-      <c r="I24" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="42"/>
+      <c r="J24" s="60"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -2476,14 +2513,14 @@
       <c r="B25" s="5">
         <v>6</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="44"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="70"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -2509,14 +2546,14 @@
       <c r="B26" s="5">
         <v>6</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="44"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="70"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -2542,14 +2579,14 @@
       <c r="B27" s="5">
         <v>6</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="44"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="70"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -2575,14 +2612,14 @@
       <c r="B28" s="5">
         <v>6</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="63"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -2608,24 +2645,24 @@
       <c r="B29" s="5">
         <v>6</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="E29" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="F29" s="52"/>
+      <c r="G29" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="41" t="s">
+      <c r="H29" s="60"/>
+      <c r="I29" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="H29" s="42"/>
-      <c r="I29" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" s="42"/>
+      <c r="J29" s="60"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -2651,14 +2688,14 @@
       <c r="B30" s="5">
         <v>6</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="44"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="70"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -2684,14 +2721,14 @@
       <c r="B31" s="5">
         <v>5</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="46"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="63"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -2717,24 +2754,24 @@
       <c r="B32" s="5">
         <v>5</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="E32" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="F32" s="52"/>
+      <c r="G32" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="41" t="s">
+      <c r="H32" s="60"/>
+      <c r="I32" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="H32" s="42"/>
-      <c r="I32" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="J32" s="42"/>
+      <c r="J32" s="60"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -2760,14 +2797,14 @@
       <c r="B33" s="5">
         <v>5</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="44"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="70"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -2793,14 +2830,14 @@
       <c r="B34" s="5">
         <v>5</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="46"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="63"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -2826,24 +2863,24 @@
       <c r="B35" s="5">
         <v>5</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="79" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="38" t="s">
+      <c r="E35" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="F35" s="52"/>
+      <c r="G35" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="39"/>
-      <c r="G35" s="41" t="s">
+      <c r="H35" s="60"/>
+      <c r="I35" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="H35" s="42"/>
-      <c r="I35" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="J35" s="42"/>
+      <c r="J35" s="60"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -2869,14 +2906,14 @@
       <c r="B36" s="5">
         <v>5</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="44"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="70"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -2902,14 +2939,14 @@
       <c r="B37" s="5">
         <v>5</v>
       </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="44"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="70"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -2935,14 +2972,14 @@
       <c r="B38" s="7">
         <v>5</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="46"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="63"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -2963,7 +3000,7 @@
     </row>
     <row r="39" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="9">
         <f>SUM(B8:B38)</f>
@@ -2973,10 +3010,10 @@
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="48"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="40"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -3083,16 +3120,16 @@
       <c r="AA42" s="3"/>
     </row>
     <row r="43" spans="1:27" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="A43" s="49" t="s">
-        <v>59</v>
+      <c r="A43" s="53" t="s">
+        <v>58</v>
       </c>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="51"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -3114,16 +3151,16 @@
       <c r="AA43" s="3"/>
     </row>
     <row r="44" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="52" t="s">
-        <v>60</v>
+      <c r="A44" s="81" t="s">
+        <v>59</v>
       </c>
-      <c r="B44" s="53"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="42"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="60"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -3145,14 +3182,14 @@
       <c r="AA44" s="3"/>
     </row>
     <row r="45" spans="1:27" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="43"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="44"/>
+      <c r="A45" s="69"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="70"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -3174,14 +3211,14 @@
       <c r="AA45" s="3"/>
     </row>
     <row r="46" spans="1:27" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="43"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="44"/>
+      <c r="A46" s="69"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="70"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
@@ -3203,14 +3240,14 @@
       <c r="AA46" s="3"/>
     </row>
     <row r="47" spans="1:27" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="43"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="44"/>
+      <c r="A47" s="69"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="70"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -3232,14 +3269,14 @@
       <c r="AA47" s="3"/>
     </row>
     <row r="48" spans="1:27" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="45"/>
-      <c r="B48" s="55"/>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="55"/>
-      <c r="H48" s="46"/>
+      <c r="A48" s="61"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="63"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
@@ -3261,16 +3298,16 @@
       <c r="AA48" s="3"/>
     </row>
     <row r="49" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="78" t="s">
-        <v>61</v>
+      <c r="A49" s="68" t="s">
+        <v>60</v>
       </c>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="42"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="60"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -3292,14 +3329,14 @@
       <c r="AA49" s="3"/>
     </row>
     <row r="50" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="43"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="44"/>
+      <c r="A50" s="69"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="70"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -3321,14 +3358,14 @@
       <c r="AA50" s="3"/>
     </row>
     <row r="51" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="43"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="44"/>
+      <c r="A51" s="69"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="70"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -3350,14 +3387,14 @@
       <c r="AA51" s="3"/>
     </row>
     <row r="52" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="43"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="44"/>
+      <c r="A52" s="69"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="70"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
@@ -3379,14 +3416,14 @@
       <c r="AA52" s="3"/>
     </row>
     <row r="53" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="43"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="44"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="70"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -3408,14 +3445,14 @@
       <c r="AA53" s="3"/>
     </row>
     <row r="54" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="45"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="55"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="55"/>
-      <c r="H54" s="46"/>
+      <c r="A54" s="61"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="63"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
@@ -3437,16 +3474,16 @@
       <c r="AA54" s="3"/>
     </row>
     <row r="55" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="78" t="s">
-        <v>62</v>
+      <c r="A55" s="68" t="s">
+        <v>61</v>
       </c>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="42"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="60"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
@@ -3468,14 +3505,14 @@
       <c r="AA55" s="3"/>
     </row>
     <row r="56" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="43"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="44"/>
+      <c r="A56" s="69"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="70"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
@@ -3497,14 +3534,14 @@
       <c r="AA56" s="3"/>
     </row>
     <row r="57" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
-      <c r="D57" s="54"/>
-      <c r="E57" s="54"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="54"/>
-      <c r="H57" s="44"/>
+      <c r="A57" s="69"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="70"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
@@ -3526,14 +3563,14 @@
       <c r="AA57" s="3"/>
     </row>
     <row r="58" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="43"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
-      <c r="D58" s="54"/>
-      <c r="E58" s="54"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="44"/>
+      <c r="A58" s="69"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="70"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -3555,14 +3592,14 @@
       <c r="AA58" s="3"/>
     </row>
     <row r="59" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="43"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
-      <c r="D59" s="54"/>
-      <c r="E59" s="54"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="44"/>
+      <c r="A59" s="69"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="70"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
@@ -3584,14 +3621,14 @@
       <c r="AA59" s="3"/>
     </row>
     <row r="60" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="43"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="44"/>
+      <c r="A60" s="69"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="70"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -3613,14 +3650,14 @@
       <c r="AA60" s="3"/>
     </row>
     <row r="61" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="45"/>
-      <c r="B61" s="55"/>
-      <c r="C61" s="55"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="55"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="55"/>
-      <c r="H61" s="46"/>
+      <c r="A61" s="61"/>
+      <c r="B61" s="62"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="62"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="63"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
@@ -3642,14 +3679,14 @@
       <c r="AA61" s="3"/>
     </row>
     <row r="62" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A62" s="79"/>
-      <c r="B62" s="57"/>
-      <c r="C62" s="57"/>
-      <c r="D62" s="57"/>
-      <c r="E62" s="57"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
+      <c r="A62" s="71"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -3671,16 +3708,16 @@
       <c r="AA62" s="3"/>
     </row>
     <row r="63" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="80" t="s">
-        <v>63</v>
+      <c r="A63" s="72" t="s">
+        <v>62</v>
       </c>
-      <c r="B63" s="57"/>
-      <c r="C63" s="57"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="48"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="40"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
@@ -3702,22 +3739,22 @@
       <c r="AA63" s="3"/>
     </row>
     <row r="64" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="74" t="s">
+      <c r="A64" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="59"/>
+      <c r="C64" s="60"/>
+      <c r="D64" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="53"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="81" t="s">
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="60"/>
+      <c r="H64" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="53"/>
-      <c r="F64" s="53"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I64" s="89"/>
-      <c r="J64" s="54"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="57"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
@@ -3737,18 +3774,18 @@
       <c r="AA64" s="3"/>
     </row>
     <row r="65" spans="1:27" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A65" s="45"/>
-      <c r="B65" s="55"/>
-      <c r="C65" s="46"/>
-      <c r="D65" s="82"/>
-      <c r="E65" s="83"/>
-      <c r="F65" s="83"/>
-      <c r="G65" s="84"/>
+      <c r="A65" s="61"/>
+      <c r="B65" s="62"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="74"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="76"/>
       <c r="H65" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
-      <c r="I65" s="89"/>
-      <c r="J65" s="54"/>
+      <c r="I65" s="56"/>
+      <c r="J65" s="57"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
@@ -3768,22 +3805,22 @@
       <c r="AA65" s="3"/>
     </row>
     <row r="66" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="85" t="s">
+      <c r="A66" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="75" t="s">
+      <c r="C66" s="63"/>
+      <c r="D66" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="90" t="s">
-        <v>70</v>
-      </c>
-      <c r="E66" s="57"/>
-      <c r="F66" s="48"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="40"/>
       <c r="G66" s="16"/>
       <c r="H66" s="17"/>
-      <c r="I66" s="89"/>
-      <c r="J66" s="54"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="57"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
@@ -3803,20 +3840,20 @@
       <c r="AA66" s="3"/>
     </row>
     <row r="67" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="39"/>
-      <c r="B67" s="77" t="s">
+      <c r="A67" s="52"/>
+      <c r="B67" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="40"/>
+      <c r="D67" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="48"/>
-      <c r="D67" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="E67" s="57"/>
-      <c r="F67" s="48"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="40"/>
       <c r="G67" s="18"/>
       <c r="H67" s="17"/>
-      <c r="I67" s="89"/>
-      <c r="J67" s="54"/>
+      <c r="I67" s="56"/>
+      <c r="J67" s="57"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
@@ -3836,20 +3873,20 @@
       <c r="AA67" s="3"/>
     </row>
     <row r="68" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="39"/>
-      <c r="B68" s="77" t="s">
+      <c r="A68" s="52"/>
+      <c r="B68" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="40"/>
+      <c r="D68" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="90" t="s">
-        <v>74</v>
-      </c>
-      <c r="E68" s="57"/>
-      <c r="F68" s="48"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="40"/>
       <c r="G68" s="18"/>
       <c r="H68" s="17"/>
-      <c r="I68" s="89"/>
-      <c r="J68" s="54"/>
+      <c r="I68" s="56"/>
+      <c r="J68" s="57"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
@@ -3869,20 +3906,20 @@
       <c r="AA68" s="3"/>
     </row>
     <row r="69" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="39"/>
-      <c r="B69" s="77" t="s">
-        <v>73</v>
+      <c r="A69" s="52"/>
+      <c r="B69" s="48" t="s">
+        <v>72</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="91" t="s">
-        <v>75</v>
+      <c r="C69" s="40"/>
+      <c r="D69" s="49" t="s">
+        <v>74</v>
       </c>
-      <c r="E69" s="57"/>
-      <c r="F69" s="48"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="40"/>
       <c r="G69" s="18"/>
       <c r="H69" s="17"/>
-      <c r="I69" s="89"/>
-      <c r="J69" s="54"/>
+      <c r="I69" s="56"/>
+      <c r="J69" s="57"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
@@ -3902,20 +3939,20 @@
       <c r="AA69" s="3"/>
     </row>
     <row r="70" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="39"/>
-      <c r="B70" s="77" t="s">
+      <c r="A70" s="52"/>
+      <c r="B70" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" s="40"/>
+      <c r="D70" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="C70" s="48"/>
-      <c r="D70" s="91" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="57"/>
-      <c r="F70" s="48"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="40"/>
       <c r="G70" s="18"/>
       <c r="H70" s="17"/>
-      <c r="I70" s="89"/>
-      <c r="J70" s="54"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="57"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
@@ -3935,20 +3972,20 @@
       <c r="AA70" s="3"/>
     </row>
     <row r="71" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="39"/>
-      <c r="B71" s="77" t="s">
+      <c r="A71" s="52"/>
+      <c r="B71" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" s="40"/>
+      <c r="D71" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C71" s="48"/>
-      <c r="D71" s="90" t="s">
-        <v>79</v>
-      </c>
-      <c r="E71" s="57"/>
-      <c r="F71" s="48"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="40"/>
       <c r="G71" s="18"/>
       <c r="H71" s="17"/>
-      <c r="I71" s="89"/>
-      <c r="J71" s="54"/>
+      <c r="I71" s="56"/>
+      <c r="J71" s="57"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
@@ -3968,20 +4005,20 @@
       <c r="AA71" s="3"/>
     </row>
     <row r="72" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="39"/>
-      <c r="B72" s="77" t="s">
+      <c r="A72" s="52"/>
+      <c r="B72" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="40"/>
+      <c r="D72" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="48"/>
-      <c r="D72" s="90" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72" s="57"/>
-      <c r="F72" s="48"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="40"/>
       <c r="G72" s="18"/>
       <c r="H72" s="17"/>
-      <c r="I72" s="89"/>
-      <c r="J72" s="54"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="57"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
@@ -4001,20 +4038,20 @@
       <c r="AA72" s="3"/>
     </row>
     <row r="73" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="39"/>
-      <c r="B73" s="77" t="s">
+      <c r="A73" s="52"/>
+      <c r="B73" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="40"/>
+      <c r="D73" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="C73" s="48"/>
-      <c r="D73" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="E73" s="57"/>
-      <c r="F73" s="48"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="40"/>
       <c r="G73" s="18"/>
       <c r="H73" s="17"/>
-      <c r="I73" s="89"/>
-      <c r="J73" s="54"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="57"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
@@ -4034,20 +4071,20 @@
       <c r="AA73" s="3"/>
     </row>
     <row r="74" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="86"/>
-      <c r="B74" s="77" t="s">
+      <c r="A74" s="65"/>
+      <c r="B74" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="40"/>
+      <c r="D74" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="C74" s="48"/>
-      <c r="D74" s="90" t="s">
-        <v>85</v>
-      </c>
-      <c r="E74" s="57"/>
-      <c r="F74" s="48"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="40"/>
       <c r="G74" s="18"/>
       <c r="H74" s="17"/>
-      <c r="I74" s="89"/>
-      <c r="J74" s="54"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="57"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
@@ -4067,22 +4104,22 @@
       <c r="AA74" s="3"/>
     </row>
     <row r="75" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="92" t="s">
+      <c r="A75" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B75" s="77" t="s">
+      <c r="C75" s="40"/>
+      <c r="D75" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="C75" s="48"/>
-      <c r="D75" s="91" t="s">
-        <v>88</v>
-      </c>
-      <c r="E75" s="57"/>
-      <c r="F75" s="48"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="40"/>
       <c r="G75" s="18"/>
       <c r="H75" s="17"/>
-      <c r="I75" s="89"/>
-      <c r="J75" s="54"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="57"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
@@ -4102,20 +4139,20 @@
       <c r="AA75" s="3"/>
     </row>
     <row r="76" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="39"/>
-      <c r="B76" s="77" t="s">
+      <c r="A76" s="52"/>
+      <c r="B76" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76" s="40"/>
+      <c r="D76" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="48"/>
-      <c r="D76" s="91" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" s="57"/>
-      <c r="F76" s="48"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="40"/>
       <c r="G76" s="18"/>
       <c r="H76" s="17"/>
-      <c r="I76" s="89"/>
-      <c r="J76" s="54"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="57"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
@@ -4135,20 +4172,20 @@
       <c r="AA76" s="3"/>
     </row>
     <row r="77" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="39"/>
-      <c r="B77" s="77" t="s">
+      <c r="A77" s="52"/>
+      <c r="B77" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C77" s="40"/>
+      <c r="D77" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="48"/>
-      <c r="D77" s="91" t="s">
-        <v>92</v>
-      </c>
-      <c r="E77" s="57"/>
-      <c r="F77" s="48"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="40"/>
       <c r="G77" s="18"/>
       <c r="H77" s="17"/>
-      <c r="I77" s="89"/>
-      <c r="J77" s="54"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="57"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
@@ -4168,20 +4205,20 @@
       <c r="AA77" s="3"/>
     </row>
     <row r="78" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="39"/>
-      <c r="B78" s="77" t="s">
-        <v>91</v>
+      <c r="A78" s="52"/>
+      <c r="B78" s="48" t="s">
+        <v>90</v>
       </c>
-      <c r="C78" s="48"/>
-      <c r="D78" s="91" t="s">
-        <v>93</v>
+      <c r="C78" s="40"/>
+      <c r="D78" s="49" t="s">
+        <v>92</v>
       </c>
-      <c r="E78" s="57"/>
-      <c r="F78" s="48"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="40"/>
       <c r="G78" s="18"/>
       <c r="H78" s="17"/>
-      <c r="I78" s="89"/>
-      <c r="J78" s="54"/>
+      <c r="I78" s="56"/>
+      <c r="J78" s="57"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
@@ -4201,20 +4238,20 @@
       <c r="AA78" s="3"/>
     </row>
     <row r="79" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="40"/>
-      <c r="B79" s="77" t="s">
+      <c r="A79" s="44"/>
+      <c r="B79" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" s="40"/>
+      <c r="D79" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="48"/>
-      <c r="D79" s="91" t="s">
-        <v>95</v>
-      </c>
-      <c r="E79" s="57"/>
-      <c r="F79" s="48"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="40"/>
       <c r="G79" s="18"/>
       <c r="H79" s="17"/>
-      <c r="I79" s="89"/>
-      <c r="J79" s="54"/>
+      <c r="I79" s="56"/>
+      <c r="J79" s="57"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
@@ -4242,8 +4279,8 @@
       <c r="F80" s="19"/>
       <c r="G80" s="19"/>
       <c r="H80" s="19"/>
-      <c r="I80" s="89"/>
-      <c r="J80" s="54"/>
+      <c r="I80" s="56"/>
+      <c r="J80" s="57"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
@@ -4263,20 +4300,20 @@
       <c r="AA80" s="3"/>
     </row>
     <row r="81" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="94" t="s">
+      <c r="A81" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B81" s="39"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="39"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="B81" s="57"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="G81" s="57"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="89"/>
-      <c r="J81" s="54"/>
+      <c r="G81" s="39"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="56"/>
+      <c r="J81" s="57"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
@@ -4299,19 +4336,19 @@
       <c r="A82" s="20">
         <v>5</v>
       </c>
-      <c r="B82" s="95" t="s">
-        <v>98</v>
+      <c r="B82" s="42" t="s">
+        <v>97</v>
       </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="93">
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="41">
         <v>100</v>
       </c>
-      <c r="G82" s="57"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="89"/>
-      <c r="J82" s="54"/>
+      <c r="G82" s="39"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="57"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
@@ -4334,19 +4371,19 @@
       <c r="A83" s="20">
         <v>4</v>
       </c>
-      <c r="B83" s="95" t="s">
-        <v>99</v>
+      <c r="B83" s="42" t="s">
+        <v>98</v>
       </c>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="93">
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="41">
         <v>80</v>
       </c>
-      <c r="G83" s="57"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="89"/>
-      <c r="J83" s="54"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="56"/>
+      <c r="J83" s="57"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
@@ -4369,19 +4406,19 @@
       <c r="A84" s="20">
         <v>3</v>
       </c>
-      <c r="B84" s="95" t="s">
-        <v>100</v>
+      <c r="B84" s="42" t="s">
+        <v>99</v>
       </c>
-      <c r="C84" s="57"/>
-      <c r="D84" s="57"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="93">
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="41">
         <v>65</v>
       </c>
-      <c r="G84" s="57"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="89"/>
-      <c r="J84" s="54"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="57"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
@@ -4404,19 +4441,19 @@
       <c r="A85" s="20">
         <v>2</v>
       </c>
-      <c r="B85" s="96" t="s">
-        <v>101</v>
+      <c r="B85" s="38" t="s">
+        <v>100</v>
       </c>
-      <c r="C85" s="57"/>
-      <c r="D85" s="57"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="93">
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="41">
         <v>50</v>
       </c>
-      <c r="G85" s="57"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="89"/>
-      <c r="J85" s="54"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="57"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
@@ -4439,19 +4476,19 @@
       <c r="A86" s="20">
         <v>1</v>
       </c>
-      <c r="B86" s="95" t="s">
-        <v>102</v>
+      <c r="B86" s="42" t="s">
+        <v>101</v>
       </c>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="93">
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="41">
         <v>30</v>
       </c>
-      <c r="G86" s="57"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="89"/>
-      <c r="J86" s="54"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="56"/>
+      <c r="J86" s="57"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
@@ -4504,13 +4541,13 @@
       <c r="B88" s="24"/>
       <c r="C88" s="25"/>
       <c r="D88" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E88" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="F88" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="F88" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="G88" s="23"/>
       <c r="H88" s="23"/>
@@ -4539,19 +4576,19 @@
       <c r="B89" s="24"/>
       <c r="C89" s="25"/>
       <c r="D89" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E89" s="43">
+        <v>1</v>
+      </c>
+      <c r="F89" s="43">
+        <v>0</v>
+      </c>
+      <c r="G89" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="E89" s="97">
-        <v>1</v>
-      </c>
-      <c r="F89" s="97">
-        <v>0</v>
-      </c>
-      <c r="G89" s="98" t="s">
+      <c r="H89" s="46" t="s">
         <v>107</v>
-      </c>
-      <c r="H89" s="99" t="s">
-        <v>108</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
@@ -4578,12 +4615,12 @@
       <c r="B90" s="24"/>
       <c r="C90" s="25"/>
       <c r="D90" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
-      <c r="E90" s="40"/>
-      <c r="F90" s="40"/>
-      <c r="G90" s="40"/>
-      <c r="H90" s="40"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44"/>
+      <c r="G90" s="44"/>
+      <c r="H90" s="44"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
@@ -4663,16 +4700,16 @@
       <c r="AA92" s="3"/>
     </row>
     <row r="93" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="49" t="s">
-        <v>59</v>
+      <c r="A93" s="53" t="s">
+        <v>58</v>
       </c>
-      <c r="B93" s="50"/>
-      <c r="C93" s="50"/>
-      <c r="D93" s="50"/>
-      <c r="E93" s="50"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
-      <c r="H93" s="51"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="55"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -4694,16 +4731,16 @@
       <c r="AA93" s="3"/>
     </row>
     <row r="94" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="52" t="s">
-        <v>110</v>
+      <c r="A94" s="81" t="s">
+        <v>109</v>
       </c>
-      <c r="B94" s="53"/>
-      <c r="C94" s="53"/>
-      <c r="D94" s="53"/>
-      <c r="E94" s="53"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="42"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="59"/>
+      <c r="E94" s="59"/>
+      <c r="F94" s="59"/>
+      <c r="G94" s="59"/>
+      <c r="H94" s="60"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
@@ -4725,14 +4762,14 @@
       <c r="AA94" s="3"/>
     </row>
     <row r="95" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="43"/>
-      <c r="B95" s="54"/>
-      <c r="C95" s="54"/>
-      <c r="D95" s="54"/>
-      <c r="E95" s="54"/>
-      <c r="F95" s="54"/>
-      <c r="G95" s="54"/>
-      <c r="H95" s="44"/>
+      <c r="A95" s="69"/>
+      <c r="B95" s="57"/>
+      <c r="C95" s="57"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="70"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
@@ -4754,14 +4791,14 @@
       <c r="AA95" s="3"/>
     </row>
     <row r="96" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="43"/>
-      <c r="B96" s="54"/>
-      <c r="C96" s="54"/>
-      <c r="D96" s="54"/>
-      <c r="E96" s="54"/>
-      <c r="F96" s="54"/>
-      <c r="G96" s="54"/>
-      <c r="H96" s="44"/>
+      <c r="A96" s="69"/>
+      <c r="B96" s="57"/>
+      <c r="C96" s="57"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="70"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
@@ -4783,14 +4820,14 @@
       <c r="AA96" s="3"/>
     </row>
     <row r="97" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="43"/>
-      <c r="B97" s="54"/>
-      <c r="C97" s="54"/>
-      <c r="D97" s="54"/>
-      <c r="E97" s="54"/>
-      <c r="F97" s="54"/>
-      <c r="G97" s="54"/>
-      <c r="H97" s="44"/>
+      <c r="A97" s="69"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="70"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
@@ -4812,14 +4849,14 @@
       <c r="AA97" s="3"/>
     </row>
     <row r="98" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="45"/>
-      <c r="B98" s="55"/>
-      <c r="C98" s="55"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="46"/>
+      <c r="A98" s="61"/>
+      <c r="B98" s="62"/>
+      <c r="C98" s="62"/>
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="63"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
@@ -4841,16 +4878,16 @@
       <c r="AA98" s="3"/>
     </row>
     <row r="99" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="78" t="s">
-        <v>111</v>
+      <c r="A99" s="68" t="s">
+        <v>110</v>
       </c>
-      <c r="B99" s="53"/>
-      <c r="C99" s="53"/>
-      <c r="D99" s="53"/>
-      <c r="E99" s="53"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53"/>
-      <c r="H99" s="42"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="59"/>
+      <c r="D99" s="59"/>
+      <c r="E99" s="59"/>
+      <c r="F99" s="59"/>
+      <c r="G99" s="59"/>
+      <c r="H99" s="60"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
@@ -4872,14 +4909,14 @@
       <c r="AA99" s="3"/>
     </row>
     <row r="100" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="43"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="54"/>
-      <c r="D100" s="54"/>
-      <c r="E100" s="54"/>
-      <c r="F100" s="54"/>
-      <c r="G100" s="54"/>
-      <c r="H100" s="44"/>
+      <c r="A100" s="69"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="70"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
@@ -4901,14 +4938,14 @@
       <c r="AA100" s="3"/>
     </row>
     <row r="101" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="43"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="54"/>
-      <c r="D101" s="54"/>
-      <c r="E101" s="54"/>
-      <c r="F101" s="54"/>
-      <c r="G101" s="54"/>
-      <c r="H101" s="44"/>
+      <c r="A101" s="69"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="57"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="70"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
@@ -4930,14 +4967,14 @@
       <c r="AA101" s="3"/>
     </row>
     <row r="102" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="43"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="54"/>
-      <c r="D102" s="54"/>
-      <c r="E102" s="54"/>
-      <c r="F102" s="54"/>
-      <c r="G102" s="54"/>
-      <c r="H102" s="44"/>
+      <c r="A102" s="69"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="70"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
@@ -4959,14 +4996,14 @@
       <c r="AA102" s="3"/>
     </row>
     <row r="103" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="43"/>
-      <c r="B103" s="54"/>
-      <c r="C103" s="54"/>
-      <c r="D103" s="54"/>
-      <c r="E103" s="54"/>
-      <c r="F103" s="54"/>
-      <c r="G103" s="54"/>
-      <c r="H103" s="44"/>
+      <c r="A103" s="69"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="57"/>
+      <c r="E103" s="57"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="57"/>
+      <c r="H103" s="70"/>
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
@@ -4988,14 +5025,14 @@
       <c r="AA103" s="3"/>
     </row>
     <row r="104" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="45"/>
-      <c r="B104" s="55"/>
-      <c r="C104" s="55"/>
-      <c r="D104" s="55"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55"/>
-      <c r="G104" s="55"/>
-      <c r="H104" s="46"/>
+      <c r="A104" s="61"/>
+      <c r="B104" s="62"/>
+      <c r="C104" s="62"/>
+      <c r="D104" s="62"/>
+      <c r="E104" s="62"/>
+      <c r="F104" s="62"/>
+      <c r="G104" s="62"/>
+      <c r="H104" s="63"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
@@ -5017,16 +5054,16 @@
       <c r="AA104" s="3"/>
     </row>
     <row r="105" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="78" t="s">
-        <v>112</v>
+      <c r="A105" s="68" t="s">
+        <v>111</v>
       </c>
-      <c r="B105" s="53"/>
-      <c r="C105" s="53"/>
-      <c r="D105" s="53"/>
-      <c r="E105" s="53"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="42"/>
+      <c r="B105" s="59"/>
+      <c r="C105" s="59"/>
+      <c r="D105" s="59"/>
+      <c r="E105" s="59"/>
+      <c r="F105" s="59"/>
+      <c r="G105" s="59"/>
+      <c r="H105" s="60"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
@@ -5048,14 +5085,14 @@
       <c r="AA105" s="3"/>
     </row>
     <row r="106" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="43"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="54"/>
-      <c r="D106" s="54"/>
-      <c r="E106" s="54"/>
-      <c r="F106" s="54"/>
-      <c r="G106" s="54"/>
-      <c r="H106" s="44"/>
+      <c r="A106" s="69"/>
+      <c r="B106" s="57"/>
+      <c r="C106" s="57"/>
+      <c r="D106" s="57"/>
+      <c r="E106" s="57"/>
+      <c r="F106" s="57"/>
+      <c r="G106" s="57"/>
+      <c r="H106" s="70"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
@@ -5077,14 +5114,14 @@
       <c r="AA106" s="3"/>
     </row>
     <row r="107" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="43"/>
-      <c r="B107" s="54"/>
-      <c r="C107" s="54"/>
-      <c r="D107" s="54"/>
-      <c r="E107" s="54"/>
-      <c r="F107" s="54"/>
-      <c r="G107" s="54"/>
-      <c r="H107" s="44"/>
+      <c r="A107" s="69"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="57"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="57"/>
+      <c r="G107" s="57"/>
+      <c r="H107" s="70"/>
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
@@ -5106,14 +5143,14 @@
       <c r="AA107" s="3"/>
     </row>
     <row r="108" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="43"/>
-      <c r="B108" s="54"/>
-      <c r="C108" s="54"/>
-      <c r="D108" s="54"/>
-      <c r="E108" s="54"/>
-      <c r="F108" s="54"/>
-      <c r="G108" s="54"/>
-      <c r="H108" s="44"/>
+      <c r="A108" s="69"/>
+      <c r="B108" s="57"/>
+      <c r="C108" s="57"/>
+      <c r="D108" s="57"/>
+      <c r="E108" s="57"/>
+      <c r="F108" s="57"/>
+      <c r="G108" s="57"/>
+      <c r="H108" s="70"/>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
@@ -5135,14 +5172,14 @@
       <c r="AA108" s="3"/>
     </row>
     <row r="109" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="43"/>
-      <c r="B109" s="54"/>
-      <c r="C109" s="54"/>
-      <c r="D109" s="54"/>
-      <c r="E109" s="54"/>
-      <c r="F109" s="54"/>
-      <c r="G109" s="54"/>
-      <c r="H109" s="44"/>
+      <c r="A109" s="69"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="57"/>
+      <c r="E109" s="57"/>
+      <c r="F109" s="57"/>
+      <c r="G109" s="57"/>
+      <c r="H109" s="70"/>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
@@ -5164,14 +5201,14 @@
       <c r="AA109" s="3"/>
     </row>
     <row r="110" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="43"/>
-      <c r="B110" s="54"/>
-      <c r="C110" s="54"/>
-      <c r="D110" s="54"/>
-      <c r="E110" s="54"/>
-      <c r="F110" s="54"/>
-      <c r="G110" s="54"/>
-      <c r="H110" s="44"/>
+      <c r="A110" s="69"/>
+      <c r="B110" s="57"/>
+      <c r="C110" s="57"/>
+      <c r="D110" s="57"/>
+      <c r="E110" s="57"/>
+      <c r="F110" s="57"/>
+      <c r="G110" s="57"/>
+      <c r="H110" s="70"/>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
@@ -5193,14 +5230,14 @@
       <c r="AA110" s="3"/>
     </row>
     <row r="111" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="45"/>
-      <c r="B111" s="55"/>
-      <c r="C111" s="55"/>
-      <c r="D111" s="55"/>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55"/>
-      <c r="G111" s="55"/>
-      <c r="H111" s="46"/>
+      <c r="A111" s="61"/>
+      <c r="B111" s="62"/>
+      <c r="C111" s="62"/>
+      <c r="D111" s="62"/>
+      <c r="E111" s="62"/>
+      <c r="F111" s="62"/>
+      <c r="G111" s="62"/>
+      <c r="H111" s="63"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
@@ -5222,14 +5259,14 @@
       <c r="AA111" s="3"/>
     </row>
     <row r="112" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="79"/>
-      <c r="B112" s="57"/>
-      <c r="C112" s="57"/>
-      <c r="D112" s="57"/>
-      <c r="E112" s="57"/>
-      <c r="F112" s="57"/>
-      <c r="G112" s="57"/>
-      <c r="H112" s="57"/>
+      <c r="A112" s="71"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="39"/>
+      <c r="D112" s="39"/>
+      <c r="E112" s="39"/>
+      <c r="F112" s="39"/>
+      <c r="G112" s="39"/>
+      <c r="H112" s="39"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
@@ -5251,16 +5288,16 @@
       <c r="AA112" s="3"/>
     </row>
     <row r="113" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="80" t="s">
-        <v>63</v>
+      <c r="A113" s="72" t="s">
+        <v>62</v>
       </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="57"/>
-      <c r="E113" s="57"/>
-      <c r="F113" s="57"/>
-      <c r="G113" s="57"/>
-      <c r="H113" s="48"/>
+      <c r="B113" s="39"/>
+      <c r="C113" s="39"/>
+      <c r="D113" s="39"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="39"/>
+      <c r="G113" s="39"/>
+      <c r="H113" s="40"/>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
@@ -5282,19 +5319,19 @@
       <c r="AA113" s="3"/>
     </row>
     <row r="114" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="74" t="s">
+      <c r="A114" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="59"/>
+      <c r="C114" s="60"/>
+      <c r="D114" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="B114" s="53"/>
-      <c r="C114" s="42"/>
-      <c r="D114" s="81" t="s">
+      <c r="E114" s="59"/>
+      <c r="F114" s="59"/>
+      <c r="G114" s="60"/>
+      <c r="H114" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="E114" s="53"/>
-      <c r="F114" s="53"/>
-      <c r="G114" s="42"/>
-      <c r="H114" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
@@ -5317,15 +5354,15 @@
       <c r="AA114" s="3"/>
     </row>
     <row r="115" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="45"/>
-      <c r="B115" s="55"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="82"/>
-      <c r="E115" s="83"/>
-      <c r="F115" s="83"/>
-      <c r="G115" s="84"/>
+      <c r="A115" s="61"/>
+      <c r="B115" s="62"/>
+      <c r="C115" s="63"/>
+      <c r="D115" s="74"/>
+      <c r="E115" s="75"/>
+      <c r="F115" s="75"/>
+      <c r="G115" s="76"/>
       <c r="H115" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
@@ -5348,18 +5385,18 @@
       <c r="AA115" s="3"/>
     </row>
     <row r="116" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="85" t="s">
-        <v>68</v>
+      <c r="A116" s="64" t="s">
+        <v>67</v>
       </c>
-      <c r="B116" s="75" t="s">
+      <c r="B116" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="C116" s="63"/>
+      <c r="D116" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="C116" s="46"/>
-      <c r="D116" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="E116" s="57"/>
-      <c r="F116" s="48"/>
+      <c r="E116" s="39"/>
+      <c r="F116" s="40"/>
       <c r="G116" s="16"/>
       <c r="H116" s="17"/>
       <c r="I116" s="3"/>
@@ -5383,16 +5420,16 @@
       <c r="AA116" s="3"/>
     </row>
     <row r="117" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="39"/>
-      <c r="B117" s="77" t="s">
+      <c r="A117" s="52"/>
+      <c r="B117" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C117" s="40"/>
+      <c r="D117" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="C117" s="48"/>
-      <c r="D117" s="76" t="s">
-        <v>116</v>
-      </c>
-      <c r="E117" s="57"/>
-      <c r="F117" s="48"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="40"/>
       <c r="G117" s="18"/>
       <c r="H117" s="17"/>
       <c r="I117" s="3"/>
@@ -5416,16 +5453,16 @@
       <c r="AA117" s="3"/>
     </row>
     <row r="118" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="39"/>
-      <c r="B118" s="77" t="s">
+      <c r="A118" s="52"/>
+      <c r="B118" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C118" s="40"/>
+      <c r="D118" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="48"/>
-      <c r="D118" s="76" t="s">
-        <v>118</v>
-      </c>
-      <c r="E118" s="57"/>
-      <c r="F118" s="48"/>
+      <c r="E118" s="39"/>
+      <c r="F118" s="40"/>
       <c r="G118" s="18"/>
       <c r="H118" s="17"/>
       <c r="I118" s="3"/>
@@ -5449,16 +5486,16 @@
       <c r="AA118" s="3"/>
     </row>
     <row r="119" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="39"/>
-      <c r="B119" s="77" t="s">
+      <c r="A119" s="52"/>
+      <c r="B119" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C119" s="40"/>
+      <c r="D119" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="C119" s="48"/>
-      <c r="D119" s="76" t="s">
-        <v>120</v>
-      </c>
-      <c r="E119" s="57"/>
-      <c r="F119" s="48"/>
+      <c r="E119" s="39"/>
+      <c r="F119" s="40"/>
       <c r="G119" s="18"/>
       <c r="H119" s="17"/>
       <c r="I119" s="3"/>
@@ -5482,16 +5519,16 @@
       <c r="AA119" s="3"/>
     </row>
     <row r="120" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="39"/>
-      <c r="B120" s="77" t="s">
+      <c r="A120" s="52"/>
+      <c r="B120" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C120" s="40"/>
+      <c r="D120" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="C120" s="48"/>
-      <c r="D120" s="76" t="s">
-        <v>122</v>
-      </c>
-      <c r="E120" s="57"/>
-      <c r="F120" s="48"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="40"/>
       <c r="G120" s="18"/>
       <c r="H120" s="17"/>
       <c r="I120" s="3"/>
@@ -5515,16 +5552,16 @@
       <c r="AA120" s="3"/>
     </row>
     <row r="121" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="39"/>
-      <c r="B121" s="77" t="s">
+      <c r="A121" s="52"/>
+      <c r="B121" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C121" s="40"/>
+      <c r="D121" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="C121" s="48"/>
-      <c r="D121" s="76" t="s">
-        <v>124</v>
-      </c>
-      <c r="E121" s="57"/>
-      <c r="F121" s="48"/>
+      <c r="E121" s="39"/>
+      <c r="F121" s="40"/>
       <c r="G121" s="18"/>
       <c r="H121" s="17"/>
       <c r="I121" s="3"/>
@@ -5548,16 +5585,16 @@
       <c r="AA121" s="3"/>
     </row>
     <row r="122" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="39"/>
-      <c r="B122" s="77" t="s">
+      <c r="A122" s="52"/>
+      <c r="B122" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C122" s="40"/>
+      <c r="D122" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="C122" s="48"/>
-      <c r="D122" s="76" t="s">
-        <v>126</v>
-      </c>
-      <c r="E122" s="57"/>
-      <c r="F122" s="48"/>
+      <c r="E122" s="39"/>
+      <c r="F122" s="40"/>
       <c r="G122" s="18"/>
       <c r="H122" s="17"/>
       <c r="I122" s="3"/>
@@ -5581,16 +5618,16 @@
       <c r="AA122" s="3"/>
     </row>
     <row r="123" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="39"/>
-      <c r="B123" s="77" t="s">
+      <c r="A123" s="52"/>
+      <c r="B123" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C123" s="40"/>
+      <c r="D123" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="C123" s="48"/>
-      <c r="D123" s="76" t="s">
-        <v>128</v>
-      </c>
-      <c r="E123" s="57"/>
-      <c r="F123" s="48"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="40"/>
       <c r="G123" s="18"/>
       <c r="H123" s="17"/>
       <c r="I123" s="3"/>
@@ -5614,16 +5651,16 @@
       <c r="AA123" s="3"/>
     </row>
     <row r="124" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="86"/>
-      <c r="B124" s="77" t="s">
+      <c r="A124" s="65"/>
+      <c r="B124" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C124" s="40"/>
+      <c r="D124" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="48"/>
-      <c r="D124" s="76" t="s">
-        <v>130</v>
-      </c>
-      <c r="E124" s="57"/>
-      <c r="F124" s="48"/>
+      <c r="E124" s="39"/>
+      <c r="F124" s="40"/>
       <c r="G124" s="18"/>
       <c r="H124" s="17"/>
       <c r="I124" s="3"/>
@@ -5648,15 +5685,15 @@
     </row>
     <row r="125" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="28"/>
-      <c r="B125" s="77" t="s">
-        <v>129</v>
+      <c r="B125" s="48" t="s">
+        <v>128</v>
       </c>
-      <c r="C125" s="48"/>
-      <c r="D125" s="76" t="s">
-        <v>131</v>
+      <c r="C125" s="40"/>
+      <c r="D125" s="50" t="s">
+        <v>130</v>
       </c>
-      <c r="E125" s="57"/>
-      <c r="F125" s="48"/>
+      <c r="E125" s="39"/>
+      <c r="F125" s="40"/>
       <c r="G125" s="18"/>
       <c r="H125" s="17"/>
       <c r="I125" s="3"/>
@@ -5680,18 +5717,18 @@
       <c r="AA125" s="3"/>
     </row>
     <row r="126" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="92" t="s">
+      <c r="A126" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B126" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B126" s="77" t="s">
-        <v>87</v>
+      <c r="C126" s="40"/>
+      <c r="D126" s="49" t="s">
+        <v>131</v>
       </c>
-      <c r="C126" s="48"/>
-      <c r="D126" s="91" t="s">
-        <v>132</v>
-      </c>
-      <c r="E126" s="57"/>
-      <c r="F126" s="48"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="40"/>
       <c r="G126" s="18"/>
       <c r="H126" s="17"/>
       <c r="I126" s="3"/>
@@ -5715,16 +5752,16 @@
       <c r="AA126" s="3"/>
     </row>
     <row r="127" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="39"/>
-      <c r="B127" s="77" t="s">
-        <v>89</v>
+      <c r="A127" s="52"/>
+      <c r="B127" s="48" t="s">
+        <v>88</v>
       </c>
-      <c r="C127" s="48"/>
-      <c r="D127" s="70" t="s">
-        <v>133</v>
+      <c r="C127" s="40"/>
+      <c r="D127" s="77" t="s">
+        <v>132</v>
       </c>
-      <c r="E127" s="57"/>
-      <c r="F127" s="48"/>
+      <c r="E127" s="39"/>
+      <c r="F127" s="40"/>
       <c r="G127" s="18"/>
       <c r="H127" s="17"/>
       <c r="I127" s="3"/>
@@ -5748,16 +5785,16 @@
       <c r="AA127" s="3"/>
     </row>
     <row r="128" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="39"/>
-      <c r="B128" s="77" t="s">
-        <v>91</v>
+      <c r="A128" s="52"/>
+      <c r="B128" s="48" t="s">
+        <v>90</v>
       </c>
-      <c r="C128" s="48"/>
-      <c r="D128" s="91" t="s">
-        <v>134</v>
+      <c r="C128" s="40"/>
+      <c r="D128" s="49" t="s">
+        <v>133</v>
       </c>
-      <c r="E128" s="57"/>
-      <c r="F128" s="48"/>
+      <c r="E128" s="39"/>
+      <c r="F128" s="40"/>
       <c r="G128" s="18"/>
       <c r="H128" s="17"/>
       <c r="I128" s="3"/>
@@ -5781,16 +5818,16 @@
       <c r="AA128" s="3"/>
     </row>
     <row r="129" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="39"/>
-      <c r="B129" s="77" t="s">
-        <v>91</v>
+      <c r="A129" s="52"/>
+      <c r="B129" s="48" t="s">
+        <v>90</v>
       </c>
-      <c r="C129" s="48"/>
-      <c r="D129" s="91" t="s">
-        <v>135</v>
+      <c r="C129" s="40"/>
+      <c r="D129" s="49" t="s">
+        <v>134</v>
       </c>
-      <c r="E129" s="57"/>
-      <c r="F129" s="48"/>
+      <c r="E129" s="39"/>
+      <c r="F129" s="40"/>
       <c r="G129" s="18"/>
       <c r="H129" s="17"/>
       <c r="I129" s="3"/>
@@ -5814,16 +5851,16 @@
       <c r="AA129" s="3"/>
     </row>
     <row r="130" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="40"/>
-      <c r="B130" s="77" t="s">
-        <v>94</v>
+      <c r="A130" s="44"/>
+      <c r="B130" s="48" t="s">
+        <v>93</v>
       </c>
-      <c r="C130" s="48"/>
-      <c r="D130" s="91" t="s">
-        <v>136</v>
+      <c r="C130" s="40"/>
+      <c r="D130" s="49" t="s">
+        <v>135</v>
       </c>
-      <c r="E130" s="57"/>
-      <c r="F130" s="48"/>
+      <c r="E130" s="39"/>
+      <c r="F130" s="40"/>
       <c r="G130" s="18"/>
       <c r="H130" s="17"/>
       <c r="I130" s="3"/>
@@ -5876,18 +5913,18 @@
       <c r="AA131" s="3"/>
     </row>
     <row r="132" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="94" t="s">
+      <c r="A132" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B132" s="39"/>
+      <c r="C132" s="39"/>
+      <c r="D132" s="39"/>
+      <c r="E132" s="40"/>
+      <c r="F132" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="B132" s="57"/>
-      <c r="C132" s="57"/>
-      <c r="D132" s="57"/>
-      <c r="E132" s="48"/>
-      <c r="F132" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="G132" s="57"/>
-      <c r="H132" s="48"/>
+      <c r="G132" s="39"/>
+      <c r="H132" s="40"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
@@ -5912,17 +5949,17 @@
       <c r="A133" s="20">
         <v>5</v>
       </c>
-      <c r="B133" s="95" t="s">
-        <v>98</v>
+      <c r="B133" s="42" t="s">
+        <v>97</v>
       </c>
-      <c r="C133" s="57"/>
-      <c r="D133" s="57"/>
-      <c r="E133" s="48"/>
-      <c r="F133" s="93">
+      <c r="C133" s="39"/>
+      <c r="D133" s="39"/>
+      <c r="E133" s="40"/>
+      <c r="F133" s="41">
         <v>100</v>
       </c>
-      <c r="G133" s="57"/>
-      <c r="H133" s="48"/>
+      <c r="G133" s="39"/>
+      <c r="H133" s="40"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -5947,17 +5984,17 @@
       <c r="A134" s="20">
         <v>4</v>
       </c>
-      <c r="B134" s="95" t="s">
-        <v>99</v>
+      <c r="B134" s="42" t="s">
+        <v>98</v>
       </c>
-      <c r="C134" s="57"/>
-      <c r="D134" s="57"/>
-      <c r="E134" s="48"/>
-      <c r="F134" s="93">
+      <c r="C134" s="39"/>
+      <c r="D134" s="39"/>
+      <c r="E134" s="40"/>
+      <c r="F134" s="41">
         <v>80</v>
       </c>
-      <c r="G134" s="57"/>
-      <c r="H134" s="48"/>
+      <c r="G134" s="39"/>
+      <c r="H134" s="40"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
@@ -5982,17 +6019,17 @@
       <c r="A135" s="20">
         <v>3</v>
       </c>
-      <c r="B135" s="95" t="s">
-        <v>100</v>
+      <c r="B135" s="42" t="s">
+        <v>99</v>
       </c>
-      <c r="C135" s="57"/>
-      <c r="D135" s="57"/>
-      <c r="E135" s="48"/>
-      <c r="F135" s="93">
+      <c r="C135" s="39"/>
+      <c r="D135" s="39"/>
+      <c r="E135" s="40"/>
+      <c r="F135" s="41">
         <v>65</v>
       </c>
-      <c r="G135" s="57"/>
-      <c r="H135" s="48"/>
+      <c r="G135" s="39"/>
+      <c r="H135" s="40"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
@@ -6017,17 +6054,17 @@
       <c r="A136" s="20">
         <v>2</v>
       </c>
-      <c r="B136" s="96" t="s">
-        <v>101</v>
+      <c r="B136" s="38" t="s">
+        <v>100</v>
       </c>
-      <c r="C136" s="57"/>
-      <c r="D136" s="57"/>
-      <c r="E136" s="48"/>
-      <c r="F136" s="93">
+      <c r="C136" s="39"/>
+      <c r="D136" s="39"/>
+      <c r="E136" s="40"/>
+      <c r="F136" s="41">
         <v>50</v>
       </c>
-      <c r="G136" s="57"/>
-      <c r="H136" s="48"/>
+      <c r="G136" s="39"/>
+      <c r="H136" s="40"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
@@ -6052,17 +6089,17 @@
       <c r="A137" s="20">
         <v>1</v>
       </c>
-      <c r="B137" s="95" t="s">
-        <v>102</v>
+      <c r="B137" s="42" t="s">
+        <v>101</v>
       </c>
-      <c r="C137" s="57"/>
-      <c r="D137" s="57"/>
-      <c r="E137" s="48"/>
-      <c r="F137" s="93">
+      <c r="C137" s="39"/>
+      <c r="D137" s="39"/>
+      <c r="E137" s="40"/>
+      <c r="F137" s="41">
         <v>30</v>
       </c>
-      <c r="G137" s="57"/>
-      <c r="H137" s="48"/>
+      <c r="G137" s="39"/>
+      <c r="H137" s="40"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
@@ -6117,13 +6154,13 @@
       <c r="B139" s="24"/>
       <c r="C139" s="25"/>
       <c r="D139" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E139" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E139" s="14" t="s">
+      <c r="F139" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="F139" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="G139" s="23"/>
       <c r="H139" s="23"/>
@@ -6152,19 +6189,19 @@
       <c r="B140" s="24"/>
       <c r="C140" s="25"/>
       <c r="D140" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E140" s="43">
+        <v>1</v>
+      </c>
+      <c r="F140" s="43">
+        <v>0</v>
+      </c>
+      <c r="G140" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="E140" s="97">
-        <v>1</v>
-      </c>
-      <c r="F140" s="97">
-        <v>0</v>
-      </c>
-      <c r="G140" s="98" t="s">
+      <c r="H140" s="46" t="s">
         <v>107</v>
-      </c>
-      <c r="H140" s="99" t="s">
-        <v>108</v>
       </c>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
@@ -6191,12 +6228,12 @@
       <c r="B141" s="24"/>
       <c r="C141" s="25"/>
       <c r="D141" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
-      <c r="E141" s="40"/>
-      <c r="F141" s="40"/>
-      <c r="G141" s="40"/>
-      <c r="H141" s="40"/>
+      <c r="E141" s="44"/>
+      <c r="F141" s="44"/>
+      <c r="G141" s="44"/>
+      <c r="H141" s="44"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
@@ -29390,151 +29427,28 @@
     </row>
   </sheetData>
   <mergeCells count="192">
-    <mergeCell ref="B136:E136"/>
-    <mergeCell ref="F136:H136"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="F137:H137"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="F140:F141"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="H140:H141"/>
-    <mergeCell ref="A132:E132"/>
-    <mergeCell ref="B133:E133"/>
-    <mergeCell ref="F133:H133"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="F134:H134"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="F135:H135"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="F132:H132"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="A126:A130"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="E89:E90"/>
-    <mergeCell ref="F89:F90"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="A75:A79"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="A64:C65"/>
-    <mergeCell ref="A66:A74"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="A49:H54"/>
-    <mergeCell ref="A55:H61"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="D64:G65"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="E35:E38"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="F11:F38"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="E15:E19"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="A114:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="A94:H98"/>
-    <mergeCell ref="A99:H104"/>
-    <mergeCell ref="A105:H111"/>
-    <mergeCell ref="A112:H112"/>
-    <mergeCell ref="A113:H113"/>
-    <mergeCell ref="D114:G115"/>
-    <mergeCell ref="A116:A124"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="G24:H28"/>
+    <mergeCell ref="I24:J28"/>
+    <mergeCell ref="G29:H31"/>
+    <mergeCell ref="I29:J31"/>
+    <mergeCell ref="I32:J34"/>
+    <mergeCell ref="G32:H34"/>
+    <mergeCell ref="G35:H38"/>
+    <mergeCell ref="I35:J38"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="B123:C123"/>
     <mergeCell ref="D123:F123"/>
     <mergeCell ref="G6:J8"/>
@@ -29552,36 +29466,159 @@
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A44:H48"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="A7:B8"/>
     <mergeCell ref="E7:F8"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="G11:H14"/>
     <mergeCell ref="G15:H19"/>
     <mergeCell ref="I15:J19"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="G5:J5"/>
     <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="F11:F38"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:F71"/>
     <mergeCell ref="D24:D28"/>
-    <mergeCell ref="G24:H28"/>
-    <mergeCell ref="I24:J28"/>
-    <mergeCell ref="G29:H31"/>
-    <mergeCell ref="I29:J31"/>
-    <mergeCell ref="I32:J34"/>
-    <mergeCell ref="G32:H34"/>
-    <mergeCell ref="G35:H38"/>
-    <mergeCell ref="I35:J38"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="A49:H54"/>
+    <mergeCell ref="A55:H61"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="D64:G65"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="A64:C65"/>
+    <mergeCell ref="A66:A74"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="A75:A79"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="F89:F90"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="A114:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="A94:H98"/>
+    <mergeCell ref="A99:H104"/>
+    <mergeCell ref="A105:H111"/>
+    <mergeCell ref="A112:H112"/>
+    <mergeCell ref="A113:H113"/>
+    <mergeCell ref="D114:G115"/>
+    <mergeCell ref="A116:A124"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="F132:H132"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="A126:A130"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="B136:E136"/>
+    <mergeCell ref="F136:H136"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="F137:H137"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="F140:F141"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="B133:E133"/>
+    <mergeCell ref="F133:H133"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="F134:H134"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="F135:H135"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
@@ -29607,16 +29644,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="100" t="s">
-        <v>137</v>
+      <c r="A1" s="118" t="s">
+        <v>136</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="30"/>
       <c r="J1" s="19"/>
       <c r="K1" s="19"/>
@@ -29637,16 +29674,16 @@
       <c r="Z1" s="19"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
-        <v>138</v>
+      <c r="A2" s="119" t="s">
+        <v>137</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="42"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60"/>
       <c r="I2" s="30"/>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
@@ -29667,14 +29704,14 @@
       <c r="Z2" s="19"/>
     </row>
     <row r="3" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="48"/>
+      <c r="A3" s="115"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
       <c r="I3" s="30"/>
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
@@ -29695,14 +29732,14 @@
       <c r="Z3" s="19"/>
     </row>
     <row r="4" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="48"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="40"/>
       <c r="I4" s="30"/>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
@@ -29723,14 +29760,14 @@
       <c r="Z4" s="19"/>
     </row>
     <row r="5" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="48"/>
+      <c r="A5" s="115"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
       <c r="I5" s="30"/>
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
@@ -29751,14 +29788,14 @@
       <c r="Z5" s="19"/>
     </row>
     <row r="6" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="48"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="30"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
@@ -29779,16 +29816,16 @@
       <c r="Z6" s="19"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="103" t="s">
-        <v>139</v>
+      <c r="A7" s="117" t="s">
+        <v>138</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="48"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="30"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
@@ -29809,14 +29846,14 @@
       <c r="Z7" s="19"/>
     </row>
     <row r="8" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="102"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="48"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="30"/>
       <c r="J8" s="19"/>
       <c r="K8" s="19"/>
@@ -29837,14 +29874,14 @@
       <c r="Z8" s="19"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="102"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="48"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="30"/>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
@@ -29865,14 +29902,14 @@
       <c r="Z9" s="19"/>
     </row>
     <row r="10" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="102"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="48"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="30"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
@@ -29893,14 +29930,14 @@
       <c r="Z10" s="19"/>
     </row>
     <row r="11" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="102"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="48"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="30"/>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
@@ -29921,14 +29958,14 @@
       <c r="Z11" s="19"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="102"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="48"/>
+      <c r="A12" s="115"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
       <c r="I12" s="30"/>
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
@@ -29949,16 +29986,16 @@
       <c r="Z12" s="19"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="103" t="s">
-        <v>140</v>
+      <c r="A13" s="117" t="s">
+        <v>139</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="48"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="31"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
@@ -29979,14 +30016,14 @@
       <c r="Z13" s="32"/>
     </row>
     <row r="14" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="102"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="48"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="30"/>
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
@@ -30007,14 +30044,14 @@
       <c r="Z14" s="19"/>
     </row>
     <row r="15" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="102"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="48"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="30"/>
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
@@ -30035,14 +30072,14 @@
       <c r="Z15" s="19"/>
     </row>
     <row r="16" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="102"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="48"/>
+      <c r="A16" s="115"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
       <c r="I16" s="30"/>
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
@@ -30063,14 +30100,14 @@
       <c r="Z16" s="19"/>
     </row>
     <row r="17" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="102"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="48"/>
+      <c r="A17" s="115"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
       <c r="I17" s="30"/>
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
@@ -30091,14 +30128,14 @@
       <c r="Z17" s="19"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="102"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="48"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
       <c r="I18" s="34"/>
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
@@ -30119,14 +30156,14 @@
       <c r="Z18" s="19"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="102"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="48"/>
+      <c r="A19" s="115"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="34"/>
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
@@ -30147,14 +30184,14 @@
       <c r="Z19" s="19"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="104"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
+      <c r="A20" s="116"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
       <c r="I20" s="30"/>
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
@@ -30175,16 +30212,16 @@
       <c r="Z20" s="19"/>
     </row>
     <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
-        <v>63</v>
+      <c r="A21" s="72" t="s">
+        <v>62</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="48"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="30"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
@@ -30205,19 +30242,19 @@
       <c r="Z21" s="19"/>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="110"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="117" t="s">
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
@@ -30238,15 +30275,15 @@
       <c r="Z22" s="19"/>
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="116"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="46"/>
+      <c r="A23" s="112"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" s="35"/>
       <c r="J23" s="19"/>
@@ -30268,16 +30305,16 @@
       <c r="Z23" s="19"/>
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="106" t="s">
-        <v>68</v>
+      <c r="A24" s="105" t="s">
+        <v>67</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="48"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H24" s="37"/>
       <c r="I24" s="35"/>
@@ -30300,14 +30337,14 @@
       <c r="Z24" s="19"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="107"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="48"/>
+      <c r="A25" s="106"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H25" s="37"/>
       <c r="J25" s="19"/>
@@ -30329,14 +30366,14 @@
       <c r="Z25" s="19"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="107"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="48"/>
+      <c r="A26" s="106"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="108"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H26" s="37"/>
       <c r="I26" s="19"/>
@@ -30359,14 +30396,14 @@
       <c r="Z26" s="19"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="107"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="48"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H27" s="37"/>
       <c r="I27" s="19"/>
@@ -30389,14 +30426,14 @@
       <c r="Z27" s="19"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="107"/>
-      <c r="B28" s="93"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="48"/>
+      <c r="A28" s="106"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H28" s="37"/>
       <c r="I28" s="19"/>
@@ -30419,14 +30456,14 @@
       <c r="Z28" s="19"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="107"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="48"/>
+      <c r="A29" s="106"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H29" s="37"/>
       <c r="I29" s="19"/>
@@ -30449,14 +30486,14 @@
       <c r="Z29" s="19"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="107"/>
-      <c r="B30" s="93"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="48"/>
+      <c r="A30" s="106"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H30" s="37"/>
       <c r="I30" s="19"/>
@@ -30479,14 +30516,14 @@
       <c r="Z30" s="19"/>
     </row>
     <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="107"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="48"/>
+      <c r="A31" s="106"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H31" s="37"/>
       <c r="I31" s="19"/>
@@ -30509,14 +30546,14 @@
       <c r="Z31" s="19"/>
     </row>
     <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="107"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="48"/>
+      <c r="A32" s="106"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H32" s="37"/>
       <c r="I32" s="19"/>
@@ -30539,14 +30576,14 @@
       <c r="Z32" s="19"/>
     </row>
     <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="108"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="48"/>
+      <c r="A33" s="107"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="40"/>
       <c r="G33" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H33" s="37"/>
       <c r="I33" s="19"/>
@@ -30569,16 +30606,16 @@
       <c r="Z33" s="19"/>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="106" t="s">
-        <v>86</v>
+      <c r="A34" s="105" t="s">
+        <v>85</v>
       </c>
-      <c r="B34" s="93"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="48"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="40"/>
       <c r="G34" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="37"/>
       <c r="I34" s="19"/>
@@ -30601,14 +30638,14 @@
       <c r="Z34" s="19"/>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="107"/>
-      <c r="B35" s="93"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="48"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H35" s="37"/>
       <c r="I35" s="19"/>
@@ -30631,14 +30668,14 @@
       <c r="Z35" s="19"/>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="107"/>
-      <c r="B36" s="93"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="48"/>
+      <c r="A36" s="106"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H36" s="37"/>
       <c r="I36" s="19"/>
@@ -30661,14 +30698,14 @@
       <c r="Z36" s="19"/>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="107"/>
-      <c r="B37" s="93"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="48"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H37" s="37"/>
       <c r="I37" s="19"/>
@@ -30691,14 +30728,14 @@
       <c r="Z37" s="19"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="108"/>
-      <c r="B38" s="93"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="48"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H38" s="37"/>
       <c r="I38" s="19"/>
@@ -30749,18 +30786,18 @@
       <c r="Z39" s="19"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="94" t="s">
+      <c r="A40" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="G40" s="57"/>
-      <c r="H40" s="48"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="40"/>
       <c r="I40" s="30"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
@@ -30784,17 +30821,17 @@
       <c r="A41" s="20">
         <v>5</v>
       </c>
-      <c r="B41" s="109" t="s">
-        <v>98</v>
+      <c r="B41" s="101" t="s">
+        <v>97</v>
       </c>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="111">
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="102">
         <v>100</v>
       </c>
-      <c r="G41" s="55"/>
-      <c r="H41" s="46"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="63"/>
       <c r="I41" s="30"/>
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
@@ -30818,17 +30855,17 @@
       <c r="A42" s="20">
         <v>4</v>
       </c>
-      <c r="B42" s="109" t="s">
-        <v>99</v>
+      <c r="B42" s="101" t="s">
+        <v>98</v>
       </c>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="111">
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="102">
         <v>80</v>
       </c>
-      <c r="G42" s="55"/>
-      <c r="H42" s="46"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="63"/>
       <c r="I42" s="30"/>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
@@ -30852,17 +30889,17 @@
       <c r="A43" s="20">
         <v>3</v>
       </c>
-      <c r="B43" s="109" t="s">
-        <v>100</v>
+      <c r="B43" s="101" t="s">
+        <v>99</v>
       </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="111">
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="102">
         <v>65</v>
       </c>
-      <c r="G43" s="55"/>
-      <c r="H43" s="46"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="63"/>
       <c r="I43" s="30"/>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
@@ -30886,17 +30923,17 @@
       <c r="A44" s="20">
         <v>2</v>
       </c>
-      <c r="B44" s="110" t="s">
-        <v>101</v>
+      <c r="B44" s="103" t="s">
+        <v>100</v>
       </c>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="111">
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="102">
         <v>50</v>
       </c>
-      <c r="G44" s="55"/>
-      <c r="H44" s="46"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="63"/>
       <c r="I44" s="30"/>
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
@@ -30920,17 +30957,17 @@
       <c r="A45" s="20">
         <v>1</v>
       </c>
-      <c r="B45" s="109" t="s">
-        <v>102</v>
+      <c r="B45" s="101" t="s">
+        <v>101</v>
       </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="111">
+      <c r="C45" s="62"/>
+      <c r="D45" s="62"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="102">
         <v>30</v>
       </c>
-      <c r="G45" s="55"/>
-      <c r="H45" s="46"/>
+      <c r="G45" s="62"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="30"/>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
@@ -30983,13 +31020,13 @@
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="F47" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="G47" s="23"/>
       <c r="H47" s="23"/>
@@ -31017,19 +31054,19 @@
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E48" s="104">
+        <v>1</v>
+      </c>
+      <c r="F48" s="104">
+        <v>0</v>
+      </c>
+      <c r="G48" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="E48" s="112">
-        <v>1</v>
-      </c>
-      <c r="F48" s="112">
-        <v>0</v>
-      </c>
-      <c r="G48" s="98" t="s">
+      <c r="H48" s="46" t="s">
         <v>107</v>
-      </c>
-      <c r="H48" s="99" t="s">
-        <v>108</v>
       </c>
       <c r="I48" s="30"/>
       <c r="J48" s="19"/>
@@ -31055,12 +31092,12 @@
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
       <c r="I49" s="30"/>
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
@@ -36910,31 +36947,38 @@
     <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A22:C23"/>
+    <mergeCell ref="D22:G23"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B29:C29"/>
@@ -36949,38 +36993,31 @@
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A22:C23"/>
-    <mergeCell ref="D22:G23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F42:H42"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
